--- a/artfynd/A 52315-2023 artfynd.xlsx
+++ b/artfynd/A 52315-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52315-2023 artfynd.xlsx
+++ b/artfynd/A 52315-2023 artfynd.xlsx
@@ -1812,11 +1812,11 @@
         <v>113694225</v>
       </c>
       <c r="B13" t="n">
-        <v>43639</v>
+        <v>43834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/artfynd/A 52315-2023 artfynd.xlsx
+++ b/artfynd/A 52315-2023 artfynd.xlsx
@@ -1812,7 +1812,7 @@
         <v>113694225</v>
       </c>
       <c r="B13" t="n">
-        <v>43834</v>
+        <v>43932</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
